--- a/docs/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/Unit_Test_Plan_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d79fe2bc3d7eff9/Desktop/AI_Ecommerce_project/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="438" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB3854D-0F3B-4FC7-84D9-FC6B59313BC5}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5982D511-B504-4928-A1A9-08C69155DA29}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -414,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -428,15 +428,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -447,10 +444,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -464,7 +460,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -785,39 +781,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:G20"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="26.54296875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="39.54296875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="36.6328125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="34.7265625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="9"/>
+    <col min="1" max="1" width="8.1796875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="39.54296875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="36.6328125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="34.7265625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="18.6328125" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" s="12" customFormat="1" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -837,7 +836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -857,7 +856,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -877,7 +876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -897,7 +896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -917,272 +916,271 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="17" t="s">
+    <row r="7" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+      <c r="F7" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+      <c r="F8" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
+      <c r="F9" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
+      <c r="F10" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
+      <c r="F11" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="5">
+      <c r="F12" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="5">
+      <c r="F13" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="5">
+      <c r="F14" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="5">
+      <c r="F15" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="5">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="15" t="s">
         <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="5">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="16" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
+      <c r="A20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="53" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>